--- a/tables/datas/common/#Monster-怪物表.xlsx
+++ b/tables/datas/common/#Monster-怪物表.xlsx
@@ -1038,7 +1038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="6"/>
   <cols>
     <col width="34.875" customWidth="1" min="7" max="7"/>
@@ -1080,6 +1080,11 @@
           <t>attrs</t>
         </is>
       </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1117,6 +1122,11 @@
           <t>(list#sep=|),common.MonsterAttr</t>
         </is>
       </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>(list#sep=|),int</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1154,6 +1164,11 @@
           <t>c,s</t>
         </is>
       </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1189,6 +1204,11 @@
       <c r="G4" t="inlineStr">
         <is>
           <t>属性列表</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>技能ID列表</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1234,12 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>HP=100|ATK=5|DEF=2</t>
+          <t>HP=100|ATK=5|DEF=2|AGILITY=80</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1240,7 +1265,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>HP=200|ATK=10|DEF=5</t>
+          <t>HP=200|ATK=10|DEF=5|AGILITY=100</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2|3</t>
         </is>
       </c>
     </row>
@@ -1266,7 +1296,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>HP=300|ATK=15|DEF=8</t>
+          <t>HP=300|ATK=15|DEF=8|AGILITY=130</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>12|13</t>
         </is>
       </c>
     </row>

--- a/tables/datas/common/#Monster-怪物表.xlsx
+++ b/tables/datas/common/#Monster-怪物表.xlsx
@@ -1038,7 +1038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="6"/>
   <cols>
     <col width="34.875" customWidth="1" min="7" max="7"/>
@@ -1085,6 +1085,11 @@
           <t>skills</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>drop_group_id</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1127,6 +1132,11 @@
           <t>(list#sep=|),int</t>
         </is>
       </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1169,6 +1179,11 @@
           <t>c,s</t>
         </is>
       </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1209,6 +1224,11 @@
       <c r="H4" t="inlineStr">
         <is>
           <t>技能ID列表</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>掉落组ID</t>
         </is>
       </c>
     </row>
@@ -1239,8 +1259,11 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
+          <t>2|26</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -1270,8 +1293,11 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2|3</t>
-        </is>
+          <t>2|3|27</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -1301,8 +1327,11 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>12|13</t>
-        </is>
+          <t>12|13|26|27</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/tables/datas/common/#Monster-怪物表.xlsx
+++ b/tables/datas/common/#Monster-怪物表.xlsx
@@ -1038,7 +1038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="6"/>
   <cols>
     <col width="34.875" customWidth="1" min="7" max="7"/>
@@ -1245,16 +1245,12 @@
         <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>10</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>1001:1</t>
-        </is>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>HP=100|ATK=5|DEF=2|AGILITY=80</t>
+          <t>HP=50|ATK=4|DEF=1|AGILITY=80</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1279,16 +1275,12 @@
         <v>2</v>
       </c>
       <c r="E6" t="n">
-        <v>20</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>1001:2</t>
-        </is>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>HP=200|ATK=10|DEF=5|AGILITY=100</t>
+          <t>HP=66|ATK=6|DEF=2|AGILITY=91</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1313,16 +1305,12 @@
         <v>3</v>
       </c>
       <c r="E7" t="n">
-        <v>30</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>1002:1</t>
-        </is>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>HP=300|ATK=15|DEF=8|AGILITY=130</t>
+          <t>HP=67|ATK=6|DEF=2|AGILITY=104</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1332,6 +1320,246 @@
       </c>
       <c r="I7" t="n">
         <v>3</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="n">
+        <v>4</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>巨型蜘蛛</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>5</v>
+      </c>
+      <c r="E8" t="n">
+        <v>60</v>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>HP=77|ATK=7|DEF=2|AGILITY=93</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>2|26|27</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="n">
+        <v>5</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>骷髅兵</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>8</v>
+      </c>
+      <c r="E9" t="n">
+        <v>96</v>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>HP=122|ATK=12|DEF=5|AGILITY=108</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>2|3|12|27</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="n">
+        <v>6</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>暗影狼</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>10</v>
+      </c>
+      <c r="E10" t="n">
+        <v>120</v>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>HP=168|ATK=18|DEF=7|AGILITY=130</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>12|13|26|27</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="n">
+        <v>7</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>山贼</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>13</v>
+      </c>
+      <c r="E11" t="n">
+        <v>156</v>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>HP=217|ATK=25|DEF=11|AGILITY=146</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>2|3|12|26|27</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="n">
+        <v>8</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>岩石巨人</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>16</v>
+      </c>
+      <c r="E12" t="n">
+        <v>192</v>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>HP=381|ATK=30|DEF=19|AGILITY=99</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>12|13|27</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="n">
+        <v>9</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>双头龙</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>20</v>
+      </c>
+      <c r="E13" t="n">
+        <v>240</v>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>HP=525|ATK=52|DEF=24|AGILITY=214</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>12|13|26|27</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="n">
+        <v>10</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>深渊恶魔</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>25</v>
+      </c>
+      <c r="E14" t="n">
+        <v>300</v>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>HP=754|ATK=84|DEF=36|AGILITY=240</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>2|3|12|13|27</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="n">
+        <v>11</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>混沌领主</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>30</v>
+      </c>
+      <c r="E15" t="n">
+        <v>360</v>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>HP=1311|ATK=120|DEF=58|AGILITY=355</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>12|13|26|27</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/tables/datas/common/#Monster-怪物表.xlsx
+++ b/tables/datas/common/#Monster-怪物表.xlsx
@@ -1129,7 +1129,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(list#sep=|),int</t>
+          <t>(list#sep=|),ESkillId</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -1247,7 +1247,6 @@
       <c r="E5" t="n">
         <v>12</v>
       </c>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>HP=50|ATK=4|DEF=1|AGILITY=80</t>
@@ -1255,7 +1254,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2|26</t>
+          <t>烈斩|猛毒撕咬</t>
         </is>
       </c>
       <c r="I5" t="n">
@@ -1277,7 +1276,6 @@
       <c r="E6" t="n">
         <v>24</v>
       </c>
-      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
           <t>HP=66|ATK=6|DEF=2|AGILITY=91</t>
@@ -1285,7 +1283,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2|3|27</t>
+          <t>烈斩|盾击|寒冰吐息</t>
         </is>
       </c>
       <c r="I6" t="n">
@@ -1307,7 +1305,6 @@
       <c r="E7" t="n">
         <v>36</v>
       </c>
-      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
           <t>HP=67|ATK=6|DEF=2|AGILITY=104</t>
@@ -1315,7 +1312,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>12|13|26|27</t>
+          <t>撕咬|狼嚎|猛毒撕咬|寒冰吐息</t>
         </is>
       </c>
       <c r="I7" t="n">
@@ -1337,7 +1334,6 @@
       <c r="E8" t="n">
         <v>60</v>
       </c>
-      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
           <t>HP=77|ATK=7|DEF=2|AGILITY=93</t>
@@ -1345,7 +1341,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2|26|27</t>
+          <t>烈斩|猛毒撕咬|寒冰吐息</t>
         </is>
       </c>
       <c r="I8" t="n">
@@ -1367,7 +1363,6 @@
       <c r="E9" t="n">
         <v>96</v>
       </c>
-      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
           <t>HP=122|ATK=12|DEF=5|AGILITY=108</t>
@@ -1375,7 +1370,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2|3|12|27</t>
+          <t>烈斩|盾击|撕咬|寒冰吐息</t>
         </is>
       </c>
       <c r="I9" t="n">
@@ -1397,7 +1392,6 @@
       <c r="E10" t="n">
         <v>120</v>
       </c>
-      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
           <t>HP=168|ATK=18|DEF=7|AGILITY=130</t>
@@ -1405,7 +1399,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>12|13|26|27</t>
+          <t>撕咬|狼嚎|猛毒撕咬|寒冰吐息</t>
         </is>
       </c>
       <c r="I10" t="n">
@@ -1427,7 +1421,6 @@
       <c r="E11" t="n">
         <v>156</v>
       </c>
-      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
           <t>HP=217|ATK=25|DEF=11|AGILITY=146</t>
@@ -1435,7 +1428,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2|3|12|26|27</t>
+          <t>烈斩|盾击|撕咬|猛毒撕咬|寒冰吐息</t>
         </is>
       </c>
       <c r="I11" t="n">
@@ -1457,7 +1450,6 @@
       <c r="E12" t="n">
         <v>192</v>
       </c>
-      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
           <t>HP=381|ATK=30|DEF=19|AGILITY=99</t>
@@ -1465,7 +1457,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>12|13|27</t>
+          <t>撕咬|狼嚎|寒冰吐息</t>
         </is>
       </c>
       <c r="I12" t="n">
@@ -1487,7 +1479,6 @@
       <c r="E13" t="n">
         <v>240</v>
       </c>
-      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
           <t>HP=525|ATK=52|DEF=24|AGILITY=214</t>
@@ -1495,7 +1486,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>12|13|26|27</t>
+          <t>撕咬|狼嚎|猛毒撕咬|寒冰吐息</t>
         </is>
       </c>
       <c r="I13" t="n">
@@ -1517,7 +1508,6 @@
       <c r="E14" t="n">
         <v>300</v>
       </c>
-      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
           <t>HP=754|ATK=84|DEF=36|AGILITY=240</t>
@@ -1525,7 +1515,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2|3|12|13|27</t>
+          <t>烈斩|盾击|撕咬|狼嚎|寒冰吐息</t>
         </is>
       </c>
       <c r="I14" t="n">
@@ -1547,7 +1537,6 @@
       <c r="E15" t="n">
         <v>360</v>
       </c>
-      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
           <t>HP=1311|ATK=120|DEF=58|AGILITY=355</t>
@@ -1555,7 +1544,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>12|13|26|27</t>
+          <t>撕咬|狼嚎|猛毒撕咬|寒冰吐息</t>
         </is>
       </c>
       <c r="I15" t="n">

--- a/tables/datas/common/#Monster-怪物表.xlsx
+++ b/tables/datas/common/#Monster-怪物表.xlsx
@@ -1038,7 +1038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="6"/>
   <cols>
     <col width="34.875" customWidth="1" min="7" max="7"/>
@@ -1551,6 +1551,64 @@
         <v>11</v>
       </c>
     </row>
+    <row r="16">
+      <c r="B16" t="n">
+        <v>12</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>野狼王</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>8</v>
+      </c>
+      <c r="E16" t="n">
+        <v>100</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>HP=180|ATK=18|DEF=6|AGILITY=115</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>撕咬|狼嚎|猛毒撕咬|寒冰吐息</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="n">
+        <v>13</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>白银野狼</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>6</v>
+      </c>
+      <c r="E17" t="n">
+        <v>80</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>HP=110|ATK=12|DEF=4|AGILITY=140</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>撕咬|猛毒撕咬</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>13</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
